--- a/excel/Debitum Rima.xlsx
+++ b/excel/Debitum Rima.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Debitum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69be8bcaca992739/Dokumentai/portfolio-analytics/portfolio-dashboard-clean/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5FC94-3329-405A-B3D0-9390BEE8EC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07CAD80-88B1-4F07-A9FE-5448FBCFD476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="K3" s="20">
         <f ca="1">'LV0000112472'!B12</f>
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="L3" s="2" t="str">
         <f ca="1">'LV0000112472'!P3</f>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="N3" s="3">
         <f>'LV0000112472'!L3</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="O3" s="3">
         <f>'LV0000112472'!M3</f>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="T3" s="30">
         <f>W3-R3</f>
-        <v>1.3000000000000114</v>
+        <v>3.0500000000000114</v>
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M100)</f>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N100)-AA3</f>
-        <v>1.2999999999999998</v>
+        <v>3.05</v>
       </c>
       <c r="W3" s="30">
         <f>Q3+S3+V3</f>
-        <v>201.3</v>
+        <v>203.05</v>
       </c>
       <c r="X3" s="30">
         <f>W3-Q3</f>
-        <v>1.3000000000000114</v>
+        <v>3.0500000000000114</v>
       </c>
       <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>6.5000000000000569E-3</v>
+        <v>1.5250000000000057E-2</v>
       </c>
       <c r="Z3" s="32">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>9.9211281538009621E-2</v>
+        <v>0.10565798878669741</v>
       </c>
       <c r="AA3" s="30">
         <f>SUM(O3:O100)</f>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="K4" s="20">
         <f ca="1">'LV0000112910'!B12</f>
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="L4" s="2" t="str">
         <f ca="1">'LV0000112910'!P3</f>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="K5" s="20">
         <f ca="1">'LV0000112886'!B12</f>
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L5" s="2" t="str">
         <f ca="1">'LV0000112886'!P3</f>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N5" s="3">
         <f>'LV0000112886'!L3</f>
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="O5" s="3">
         <f>'LV0000112886'!M3</f>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="K6" s="20">
         <f ca="1">'LV0000112894'!B12</f>
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="L6" s="2" t="str">
         <f ca="1">'LV0000112894'!P3</f>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N6" s="3">
         <f>'LV0000112894'!L3</f>
-        <v>0.14000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="O6" s="3">
         <f>'LV0000112894'!M3</f>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K7" s="20">
         <f ca="1">'LV0000112688 '!B12</f>
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="L7" s="2" t="str">
         <f ca="1">'LV0000112688 '!P3</f>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="N7" s="3">
         <f>'LV0000112688 '!L3</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="O7" s="3">
         <f>'LV0000112688 '!M3</f>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K8" s="20">
         <f ca="1">'LV0000112548'!B12</f>
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="L8" s="2" t="str">
         <f ca="1">'LV0000112548'!P3</f>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="N8" s="3">
         <f>'LV0000112548'!L3</f>
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="O8" s="3">
         <f>'LV0000112548'!M3</f>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="K9" s="20">
         <f ca="1">'LV0000112530'!B12</f>
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="L9" s="2" t="str">
         <f ca="1">'LV0000112530'!P3</f>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="N9" s="3">
         <f>'LV0000112530'!L3</f>
-        <v>0.2</v>
+        <v>0.48000000000000004</v>
       </c>
       <c r="O9" s="3">
         <f>'LV0000112530'!M3</f>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="K10" s="20">
         <f ca="1">'LV0000112076'!B12</f>
-        <v>639</v>
+        <v>609</v>
       </c>
       <c r="L10" s="2" t="str">
         <f ca="1">'LV0000112076'!P3</f>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="N10" s="3">
         <f>'LV0000112076'!L3</f>
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="O10" s="3">
         <f>'LV0000112076'!M3</f>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="K11" s="20">
         <f ca="1">'LV0000112241'!B12</f>
-        <v>675</v>
+        <v>645</v>
       </c>
       <c r="L11" s="2" t="str">
         <f ca="1">'LV0000112241'!P3</f>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="N11" s="3">
         <f>'LV0000112241'!L3</f>
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="O11" s="3">
         <f>'LV0000112241'!M3</f>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -4124,12 +4124,25 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3"/>
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.18</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -4156,11 +4169,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="0">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="1">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -4304,7 +4317,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -5162,7 +5175,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -6691,14 +6704,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>201.3</v>
+        <v>203.05</v>
       </c>
     </row>
   </sheetData>
@@ -6848,7 +6861,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -6891,15 +6904,25 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -6929,11 +6952,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -7095,7 +7118,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>675</v>
+        <v>645</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -7959,7 +7982,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -8137,7 +8160,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -8180,15 +8203,25 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -8218,11 +8251,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -8384,7 +8417,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>639</v>
+        <v>609</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -9248,7 +9281,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -9426,7 +9459,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.2</v>
+        <v>0.48000000000000004</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -9469,15 +9502,25 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -9507,11 +9550,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -9673,7 +9716,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -10537,7 +10580,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.2</v>
+        <v>0.48000000000000004</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -10715,7 +10758,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -10758,15 +10801,25 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -10796,11 +10849,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -10962,7 +11015,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -11826,7 +11879,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.21</v>
+        <v>0.51</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -12005,7 +12058,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -12048,15 +12101,25 @@
       <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -12086,11 +12149,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -12252,7 +12315,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -13116,7 +13179,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -13294,7 +13357,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.14000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -13337,15 +13400,25 @@
       <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -13375,11 +13448,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -13541,7 +13614,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -14405,7 +14478,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.14000000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
@@ -14583,7 +14656,7 @@
       </c>
       <c r="L3" s="3">
         <f>H53</f>
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="M3" s="3">
         <f>I53</f>
@@ -14626,15 +14699,25 @@
       <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="20" t="str">
+      <c r="D4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="E4" s="13">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="20">
         <f>IF(E4&gt;0,E4-D4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="X4" s="6">
         <f>E3</f>
@@ -14664,11 +14747,11 @@
       <c r="J5" s="9"/>
       <c r="X5" s="6">
         <f t="shared" ref="X5:X52" si="1">E4</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Y5" s="3">
         <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -14830,7 +14913,7 @@
       </c>
       <c r="B12" s="20">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="6"/>
@@ -15694,7 +15777,7 @@
       </c>
       <c r="H53" s="3">
         <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="3"/>
